--- a/2026/PICHINCHA/ENERO/PICHINCHA-Enero.xlsx
+++ b/2026/PICHINCHA/ENERO/PICHINCHA-Enero.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PICHINCHA\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\PICHINCHA\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B3F39D-7083-4104-B98D-6429911A8331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF30585-C3BC-425C-9A4C-DFB6E89D004D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="83">
   <si>
     <t>UF</t>
   </si>
@@ -259,9 +259,6 @@
     <t>Julio doartero - Reparacion de porton</t>
   </si>
   <si>
-    <t>Mes de octubre adeudado</t>
-  </si>
-  <si>
     <t>Prevision Ordinaria</t>
   </si>
   <si>
@@ -272,6 +269,12 @@
   </si>
   <si>
     <t>ENERO</t>
+  </si>
+  <si>
+    <t>SUBIDOS EN EN3R0</t>
+  </si>
+  <si>
+    <t>Pendiente articulos de limpieza de enero</t>
   </si>
 </sst>
 </file>
@@ -284,7 +287,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,13 +388,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1308,6 +1304,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1377,8 +1376,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1747,22 +1745,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H69"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1770,27 +1768,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1798,13 +1796,13 @@
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
       <c r="E7" s="24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7" s="111" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1812,29 +1810,29 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
+      <c r="C11" s="125"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="125" t="s">
+      <c r="E11" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="125"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="126"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="107" t="s">
         <v>64</v>
       </c>
       <c r="B12" s="108"/>
-      <c r="C12" s="148">
+      <c r="C12" s="121">
         <v>18158.46</v>
       </c>
       <c r="D12" s="5"/>
@@ -1842,16 +1840,14 @@
         <v>42</v>
       </c>
       <c r="F12" s="57">
-        <v>-279626.99777246732</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-166692.01777246734</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="108" t="s">
-        <v>77</v>
-      </c>
+      <c r="B13" s="108"/>
       <c r="C13" s="121">
         <v>0</v>
       </c>
@@ -1859,11 +1855,11 @@
       <c r="E13" s="122"/>
       <c r="F13" s="123"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="148">
+      <c r="C14" s="121">
         <v>119977</v>
       </c>
       <c r="D14" s="43"/>
@@ -1872,18 +1868,18 @@
       </c>
       <c r="F14" s="59">
         <f>'prorrateo '!F10</f>
-        <v>713950.86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>360609.52800000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="108" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="80">
-        <v>40000</v>
+        <v>42700</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="58" t="s">
@@ -1891,56 +1887,61 @@
       </c>
       <c r="F15" s="59">
         <f>-(C39)</f>
-        <v>-600921.44999999995</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>-363717.38</v>
+      </c>
+      <c r="H15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="108"/>
       <c r="C16" s="119">
-        <v>71368.7</v>
+        <v>106529.17</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="58"/>
       <c r="F16" s="59"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="s">
         <v>68</v>
       </c>
       <c r="B17" s="108"/>
       <c r="C17" s="119">
-        <v>118666.11</v>
+        <v>0</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="58"/>
       <c r="F17" s="59"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="s">
         <v>71</v>
       </c>
       <c r="C18" s="119">
-        <v>56295.43</v>
-      </c>
-      <c r="D18" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="D18" s="149" t="s">
+        <v>82</v>
+      </c>
       <c r="E18" s="58"/>
       <c r="F18" s="59"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
         <v>73</v>
       </c>
       <c r="C19" s="119">
-        <v>15103</v>
+        <v>0</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="58"/>
       <c r="F19" s="59"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
         <v>69</v>
       </c>
@@ -1951,22 +1952,22 @@
       <c r="F20" s="59"/>
       <c r="H20" s="108"/>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="32"/>
       <c r="B21" s="33"/>
       <c r="C21" s="87">
         <f>SUM(C12:C20)</f>
-        <v>439568.69999999995</v>
+        <v>287364.63</v>
       </c>
       <c r="E21" s="60" t="s">
         <v>43</v>
       </c>
       <c r="F21" s="124">
         <f>SUM(F12:F20)</f>
-        <v>-166597.58777246729</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>-169799.8697724673</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
         <v>21</v>
       </c>
@@ -1975,7 +1976,7 @@
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="s">
         <v>63</v>
       </c>
@@ -1987,19 +1988,19 @@
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="35"/>
-      <c r="C24" s="149">
+      <c r="C24" s="119">
         <v>4519.75</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
         <v>75</v>
       </c>
@@ -2011,21 +2012,19 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="127" t="s">
+    <row r="26" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="128" t="s">
         <v>76</v>
       </c>
-      <c r="B26" s="128"/>
-      <c r="C26" s="119">
-        <v>85000</v>
-      </c>
+      <c r="B26" s="129"/>
+      <c r="C26" s="119"/>
       <c r="D26" s="5"/>
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B27" s="35"/>
       <c r="C27" s="112"/>
@@ -2033,32 +2032,32 @@
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="32"/>
       <c r="B28" s="33"/>
       <c r="C28" s="109">
         <f>SUM(C22:C27)</f>
-        <v>161352.75</v>
+        <v>76352.75</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="55"/>
       <c r="G28" s="6"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="47" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="48"/>
       <c r="C29" s="49">
         <f>+C28+C21</f>
-        <v>600921.44999999995</v>
+        <v>363717.38</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
     </row>
-    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="69" t="s">
         <v>24</v>
       </c>
@@ -2067,18 +2066,18 @@
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
       <c r="B32" s="29"/>
       <c r="C32" s="54"/>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="52"/>
       <c r="B33" s="51"/>
       <c r="C33" s="53">
@@ -2086,7 +2085,7 @@
       </c>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="61"/>
       <c r="B34" s="62"/>
       <c r="C34" s="53">
@@ -2094,19 +2093,19 @@
       </c>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="78"/>
       <c r="B35" s="79"/>
       <c r="C35" s="81"/>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="78"/>
       <c r="B36" s="85"/>
       <c r="C36" s="86"/>
       <c r="F36" s="6"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="78"/>
       <c r="B37" s="84"/>
       <c r="C37" s="81">
@@ -2114,7 +2113,7 @@
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="63" t="s">
         <v>23</v>
       </c>
@@ -2124,98 +2123,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>54</v>
       </c>
       <c r="C39" s="53">
         <f>C29-C27</f>
-        <v>600921.44999999995</v>
+        <v>363717.38</v>
       </c>
       <c r="F39" s="6"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C40" s="77">
         <f>+C29</f>
-        <v>600921.44999999995</v>
+        <v>363717.38</v>
       </c>
       <c r="F40" s="6"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="63" t="s">
         <v>13</v>
       </c>
       <c r="B41" s="64"/>
       <c r="C41" s="65">
         <f>+C29+C38</f>
-        <v>600921.44999999995</v>
+        <v>363717.38</v>
       </c>
       <c r="E41" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D46" s="6"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D47" s="16"/>
       <c r="E47" s="16"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="126"/>
-      <c r="C48" s="126"/>
-      <c r="D48" s="126"/>
-      <c r="E48" s="126"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="126"/>
-      <c r="C49" s="126"/>
-      <c r="D49" s="126"/>
-      <c r="E49" s="126"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B50" s="126"/>
-      <c r="C50" s="126"/>
-      <c r="D50" s="126"/>
-      <c r="E50" s="126"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="127"/>
+      <c r="C48" s="127"/>
+      <c r="D48" s="127"/>
+      <c r="E48" s="127"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="127"/>
+      <c r="C49" s="127"/>
+      <c r="D49" s="127"/>
+      <c r="E49" s="127"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="127"/>
+      <c r="C50" s="127"/>
+      <c r="D50" s="127"/>
+      <c r="E50" s="127"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="19"/>
       <c r="B62" s="18"/>
       <c r="C62" s="20"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="18"/>
       <c r="B68" s="18"/>
       <c r="C68" s="18"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="18"/>
       <c r="B69" s="18"/>
       <c r="C69" s="18"/>
@@ -2242,25 +2241,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="105" t="s">
         <v>55</v>
       </c>
@@ -2276,12 +2275,12 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="71">
-        <v>601015.88</v>
+        <v>363717.38</v>
       </c>
       <c r="L1" s="71"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="72" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ENERO</v>
@@ -2301,7 +2300,7 @@
       <c r="L2" s="114"/>
       <c r="M2" s="76"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2342,7 +2341,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2376,7 +2375,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2388,26 +2387,23 @@
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="41">
-        <v>146163</v>
-      </c>
-      <c r="F5" s="80">
-        <f>E5</f>
-        <v>146163</v>
-      </c>
+        <v>120203.17600000001</v>
+      </c>
+      <c r="F5" s="80"/>
       <c r="G5" s="67">
         <f>E5-F5</f>
-        <v>0</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="H5" s="70">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>0</v>
+        <v>4808.1270400000003</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="38">
         <f>K$1/5</f>
-        <v>120203.17600000001</v>
+        <v>72743.475999999995</v>
       </c>
       <c r="K5" s="117">
         <f>K2*D5</f>
@@ -2415,14 +2411,14 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>120203.17600000001</v>
+        <v>197754.77903999999</v>
       </c>
       <c r="M5" s="39">
         <f>L5*4%+L5</f>
-        <v>125011.30304000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>205664.97020159999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2434,11 +2430,11 @@
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="41">
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="F6" s="80">
         <f t="shared" ref="F6:F9" si="0">E6</f>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="G6" s="67">
         <f>E6-F6</f>
@@ -2453,7 +2449,7 @@
       </c>
       <c r="J6" s="38">
         <f t="shared" ref="J6:J9" si="2">K$1/5</f>
-        <v>120203.17600000001</v>
+        <v>72743.475999999995</v>
       </c>
       <c r="K6" s="117">
         <f>K2*D6</f>
@@ -2461,14 +2457,14 @@
       </c>
       <c r="L6" s="15">
         <f>J6+K6+H6+G6</f>
-        <v>120203.17600000001</v>
+        <v>72743.475999999995</v>
       </c>
       <c r="M6" s="39">
         <f t="shared" ref="M6:M9" si="3">L6*4%+L6</f>
-        <v>125011.30304000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>75653.215039999995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2480,26 +2476,23 @@
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="41">
-        <v>146163</v>
-      </c>
-      <c r="F7" s="80">
-        <f t="shared" si="0"/>
-        <v>146163</v>
-      </c>
+        <v>120203.17600000001</v>
+      </c>
+      <c r="F7" s="80"/>
       <c r="G7" s="67">
         <f t="shared" ref="G7:G8" si="4">E7-F7</f>
-        <v>0</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="H7" s="70">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4808.1270400000003</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="38">
         <f t="shared" si="2"/>
-        <v>120203.17600000001</v>
+        <v>72743.475999999995</v>
       </c>
       <c r="K7" s="117">
         <f>K2*D7</f>
@@ -2507,14 +2500,14 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>120203.17600000001</v>
+        <v>197754.77903999999</v>
       </c>
       <c r="M7" s="39">
         <f t="shared" si="3"/>
-        <v>125011.30304000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>205664.97020159999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2526,11 +2519,11 @@
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="41">
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="F8" s="80">
         <f t="shared" si="0"/>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="G8" s="67">
         <f t="shared" si="4"/>
@@ -2545,7 +2538,7 @@
       </c>
       <c r="J8" s="38">
         <f t="shared" si="2"/>
-        <v>120203.17600000001</v>
+        <v>72743.475999999995</v>
       </c>
       <c r="K8" s="117">
         <f>K2*D8</f>
@@ -2553,14 +2546,14 @@
       </c>
       <c r="L8" s="15">
         <f>J8+K8+H8+G8</f>
-        <v>120203.17600000001</v>
+        <v>72743.475999999995</v>
       </c>
       <c r="M8" s="39">
         <f t="shared" si="3"/>
-        <v>125011.30304000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>75653.215039999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2572,11 +2565,11 @@
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="41">
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="F9" s="80">
         <f t="shared" si="0"/>
-        <v>140541.62</v>
+        <v>120203.17600000001</v>
       </c>
       <c r="G9" s="67">
         <f>E9-F9</f>
@@ -2591,7 +2584,7 @@
       </c>
       <c r="J9" s="38">
         <f t="shared" si="2"/>
-        <v>120203.17600000001</v>
+        <v>72743.475999999995</v>
       </c>
       <c r="K9" s="117">
         <f>K2*D9</f>
@@ -2599,14 +2592,14 @@
       </c>
       <c r="L9" s="15">
         <f>J9+K9+H9+G9</f>
-        <v>120203.17600000001</v>
+        <v>72743.475999999995</v>
       </c>
       <c r="M9" s="39">
         <f t="shared" si="3"/>
-        <v>125011.30304000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>75653.215039999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2618,19 +2611,19 @@
       </c>
       <c r="E10" s="42">
         <f t="shared" si="5"/>
-        <v>713950.86</v>
+        <v>601015.88</v>
       </c>
       <c r="F10" s="42">
         <f>SUM(F5:F9)</f>
-        <v>713950.86</v>
+        <v>360609.52800000005</v>
       </c>
       <c r="G10" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>240406.35200000001</v>
       </c>
       <c r="H10" s="50">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9616.2540800000006</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="5"/>
@@ -2638,7 +2631,7 @@
       </c>
       <c r="J10" s="46">
         <f t="shared" si="5"/>
-        <v>601015.88</v>
+        <v>363717.38</v>
       </c>
       <c r="K10" s="46">
         <f t="shared" si="5"/>
@@ -2646,78 +2639,78 @@
       </c>
       <c r="L10" s="118">
         <f t="shared" si="5"/>
-        <v>601015.88</v>
+        <v>613739.98607999994</v>
       </c>
       <c r="M10" s="118">
         <f t="shared" si="5"/>
-        <v>625056.51520000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="129"/>
-      <c r="B11" s="129"/>
-      <c r="C11" s="129"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="129"/>
-      <c r="I11" s="129"/>
-      <c r="J11" s="129"/>
-      <c r="K11" s="129"/>
-      <c r="L11" s="129"/>
-      <c r="M11" s="129"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>638289.58552319999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="130"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="130"/>
-      <c r="D13" s="130"/>
-      <c r="E13" s="130"/>
-      <c r="F13" s="130"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="130"/>
-      <c r="K13" s="130"/>
-      <c r="L13" s="130"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="130"/>
-      <c r="D14" s="130"/>
-      <c r="E14" s="130"/>
-      <c r="F14" s="130"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="130"/>
-      <c r="K14" s="130"/>
-      <c r="L14" s="130"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="130"/>
-      <c r="D15" s="130"/>
-      <c r="E15" s="130"/>
-      <c r="F15" s="130"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="130"/>
-      <c r="K15" s="130"/>
-      <c r="L15" s="130"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="130"/>
-      <c r="D16" s="130"/>
-      <c r="E16" s="130"/>
-      <c r="F16" s="130"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="130"/>
-      <c r="K16" s="130"/>
-      <c r="L16" s="130"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="131"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="131"/>
+      <c r="I14" s="131"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="131"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="131"/>
+      <c r="H16" s="131"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="131"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2733,68 +2726,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="136" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="139"/>
       <c r="F1" s="88"/>
       <c r="G1" s="88"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="139" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="140"/>
-      <c r="C2" s="141"/>
-      <c r="D2" s="142">
+      <c r="B2" s="141"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="143">
         <v>565</v>
       </c>
-      <c r="E2" s="143"/>
+      <c r="E2" s="144"/>
       <c r="F2" s="89"/>
       <c r="G2" s="89"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="144" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="145" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="146" t="s">
+      <c r="D3" s="147" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="131" t="s">
+      <c r="E3" s="132" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="131" t="s">
+      <c r="F3" s="132" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="131" t="s">
+      <c r="G3" s="132" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="145"/>
-      <c r="B4" s="145"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="146"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="90">
         <v>1</v>
       </c>
@@ -2817,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="90">
         <v>2</v>
       </c>
@@ -2840,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="90">
         <v>3</v>
       </c>
@@ -2863,7 +2856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="90">
         <v>4</v>
       </c>
@@ -2886,7 +2879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="90">
         <v>5</v>
       </c>
@@ -2909,7 +2902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="95">
         <v>6</v>
       </c>
@@ -2932,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="100" t="s">
         <v>8</v>
       </c>
@@ -2951,12 +2944,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="133"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="134"/>
-      <c r="D12" s="134"/>
-      <c r="E12" s="135"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="136"/>
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
     </row>
